--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2195,6 +2195,2422 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130269245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>421197</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7041597</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130269237</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>421457</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7041831</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130269221</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>421287</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7041560</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130269230</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>421457</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7041782</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130269229</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421474</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7041778</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130269253</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421511</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7041768</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130269250</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>421267</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7041668</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130269246</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>421193</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7041705</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130269232</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>421465</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7041678</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130269254</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>421471</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7041708</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130269228</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>421450</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7041763</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130269238</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>421547</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7041796</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130269227</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>421346</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7041741</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130269248</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>421263</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7041605</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130269244</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>421242</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7041553</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130269234</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91742</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>421319</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7041510</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130269247</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>421218</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7041644</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130269226</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>421267</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7041662</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130269251</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>421531</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7041803</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130269243</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>421168</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7041110</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130269231</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>421458</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7041835</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130269223</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>421322</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7041512</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130269252</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>421539</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7041777</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130269236</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>421465</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7041769</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130269237</v>
+        <v>130269245</v>
       </c>
       <c r="B15" t="n">
-        <v>91748</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,19 +2209,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2229,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421457</v>
+        <v>421197</v>
       </c>
       <c r="R15" t="n">
-        <v>7041831</v>
+        <v>7041597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,6 +2269,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130269245</v>
+        <v>130269237</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,23 +2311,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421197</v>
+        <v>421457</v>
       </c>
       <c r="R16" t="n">
-        <v>7041597</v>
+        <v>7041831</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,11 +2367,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,7 +2396,7 @@
         <v>130269253</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130269246</v>
+        <v>130269250</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421193</v>
+        <v>421267</v>
       </c>
       <c r="R21" t="n">
-        <v>7041705</v>
+        <v>7041668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130269250</v>
+        <v>130269246</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421267</v>
+        <v>421193</v>
       </c>
       <c r="R22" t="n">
-        <v>7041668</v>
+        <v>7041705</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269254</v>
+        <v>130269238</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,23 +3118,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3142,10 +3138,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421471</v>
+        <v>421547</v>
       </c>
       <c r="R24" t="n">
-        <v>7041708</v>
+        <v>7041796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3178,11 +3174,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269238</v>
+        <v>130269254</v>
       </c>
       <c r="B25" t="n">
-        <v>91748</v>
+        <v>79183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,19 +3211,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3240,10 +3235,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421547</v>
+        <v>421471</v>
       </c>
       <c r="R25" t="n">
-        <v>7041796</v>
+        <v>7041708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,6 +3271,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3509,7 +3509,7 @@
         <v>130269248</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269234</v>
+        <v>130269244</v>
       </c>
       <c r="B29" t="n">
-        <v>91742</v>
+        <v>79183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421319</v>
+        <v>421242</v>
       </c>
       <c r="R29" t="n">
-        <v>7041510</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,6 +3679,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3705,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130269244</v>
+        <v>130269234</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>91745</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421242</v>
+        <v>421319</v>
       </c>
       <c r="R30" t="n">
-        <v>7041553</v>
+        <v>7041510</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,11 +3781,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,7 +3810,7 @@
         <v>130269247</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>130269251</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>130269243</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130269252</v>
+        <v>130269236</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4226,23 +4226,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4250,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421539</v>
+        <v>421465</v>
       </c>
       <c r="R35" t="n">
-        <v>7041777</v>
+        <v>7041769</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,11 +4282,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4317,10 +4308,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269236</v>
+        <v>130269231</v>
       </c>
       <c r="B36" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4328,19 +4319,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4348,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421465</v>
+        <v>421458</v>
       </c>
       <c r="R36" t="n">
-        <v>7041769</v>
+        <v>7041835</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4384,6 +4379,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,7 +4410,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269231</v>
+        <v>130269223</v>
       </c>
       <c r="B37" t="n">
         <v>57826</v>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421458</v>
+        <v>421322</v>
       </c>
       <c r="R37" t="n">
-        <v>7041835</v>
+        <v>7041512</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,10 +4512,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269223</v>
+        <v>130269252</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421322</v>
+        <v>421539</v>
       </c>
       <c r="R38" t="n">
-        <v>7041512</v>
+        <v>7041777</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130269245</v>
+        <v>130269237</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>91777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,23 +2209,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2233,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421197</v>
+        <v>421457</v>
       </c>
       <c r="R15" t="n">
-        <v>7041597</v>
+        <v>7041831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,11 +2265,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130269237</v>
+        <v>130269245</v>
       </c>
       <c r="B16" t="n">
-        <v>91751</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2311,19 +2302,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2331,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421457</v>
+        <v>421197</v>
       </c>
       <c r="R16" t="n">
-        <v>7041831</v>
+        <v>7041597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,6 +2362,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130269253</v>
+        <v>130269221</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,21 +2404,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421511</v>
+        <v>421287</v>
       </c>
       <c r="R17" t="n">
-        <v>7041768</v>
+        <v>7041560</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130269221</v>
+        <v>130269230</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421287</v>
+        <v>421457</v>
       </c>
       <c r="R18" t="n">
-        <v>7041560</v>
+        <v>7041782</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130269230</v>
+        <v>130269229</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421457</v>
+        <v>421474</v>
       </c>
       <c r="R19" t="n">
-        <v>7041782</v>
+        <v>7041778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130269229</v>
+        <v>130269253</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421474</v>
+        <v>421511</v>
       </c>
       <c r="R20" t="n">
-        <v>7041778</v>
+        <v>7041768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,7 +2804,7 @@
         <v>130269250</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>130269246</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>130269232</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>130269238</v>
       </c>
       <c r="B24" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>130269254</v>
       </c>
       <c r="B25" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>130269228</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>130269227</v>
       </c>
       <c r="B27" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>130269248</v>
       </c>
       <c r="B28" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269244</v>
+        <v>130269234</v>
       </c>
       <c r="B29" t="n">
-        <v>79183</v>
+        <v>91771</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421242</v>
+        <v>421319</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,11 +3679,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130269234</v>
+        <v>130269247</v>
       </c>
       <c r="B30" t="n">
-        <v>91745</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,21 +3716,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421319</v>
+        <v>421218</v>
       </c>
       <c r="R30" t="n">
-        <v>7041510</v>
+        <v>7041644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,6 +3776,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3807,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130269247</v>
+        <v>130269244</v>
       </c>
       <c r="B31" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421218</v>
+        <v>421242</v>
       </c>
       <c r="R31" t="n">
-        <v>7041644</v>
+        <v>7041553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3912,7 +3912,7 @@
         <v>130269226</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130269251</v>
+        <v>130269243</v>
       </c>
       <c r="B33" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421531</v>
+        <v>421168</v>
       </c>
       <c r="R33" t="n">
-        <v>7041803</v>
+        <v>7041110</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130269243</v>
+        <v>130269251</v>
       </c>
       <c r="B34" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421168</v>
+        <v>421531</v>
       </c>
       <c r="R34" t="n">
-        <v>7041110</v>
+        <v>7041803</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4218,7 +4218,7 @@
         <v>130269236</v>
       </c>
       <c r="B35" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269231</v>
+        <v>130269252</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4319,21 +4319,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421458</v>
+        <v>421539</v>
       </c>
       <c r="R36" t="n">
-        <v>7041835</v>
+        <v>7041777</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,10 +4410,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269223</v>
+        <v>130269231</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421322</v>
+        <v>421458</v>
       </c>
       <c r="R37" t="n">
-        <v>7041512</v>
+        <v>7041835</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,10 +4512,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269252</v>
+        <v>130269223</v>
       </c>
       <c r="B38" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421539</v>
+        <v>421322</v>
       </c>
       <c r="R38" t="n">
-        <v>7041777</v>
+        <v>7041512</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130269221</v>
+        <v>130269253</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,21 +2404,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421287</v>
+        <v>421511</v>
       </c>
       <c r="R17" t="n">
-        <v>7041560</v>
+        <v>7041768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130269230</v>
+        <v>130269221</v>
       </c>
       <c r="B18" t="n">
         <v>57852</v>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421457</v>
+        <v>421287</v>
       </c>
       <c r="R18" t="n">
-        <v>7041782</v>
+        <v>7041560</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,7 +2597,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130269229</v>
+        <v>130269230</v>
       </c>
       <c r="B19" t="n">
         <v>57852</v>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421474</v>
+        <v>421457</v>
       </c>
       <c r="R19" t="n">
-        <v>7041778</v>
+        <v>7041782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130269253</v>
+        <v>130269229</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421511</v>
+        <v>421474</v>
       </c>
       <c r="R20" t="n">
-        <v>7041768</v>
+        <v>7041778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4410,7 +4410,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269231</v>
+        <v>130269223</v>
       </c>
       <c r="B37" t="n">
         <v>57852</v>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421458</v>
+        <v>421322</v>
       </c>
       <c r="R37" t="n">
-        <v>7041835</v>
+        <v>7041512</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,7 +4512,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269223</v>
+        <v>130269231</v>
       </c>
       <c r="B38" t="n">
         <v>57852</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421322</v>
+        <v>421458</v>
       </c>
       <c r="R38" t="n">
-        <v>7041512</v>
+        <v>7041835</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2201,7 +2201,7 @@
         <v>130269237</v>
       </c>
       <c r="B15" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130269253</v>
+        <v>130269221</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,21 +2404,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421511</v>
+        <v>421287</v>
       </c>
       <c r="R17" t="n">
-        <v>7041768</v>
+        <v>7041560</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130269221</v>
+        <v>130269230</v>
       </c>
       <c r="B18" t="n">
         <v>57852</v>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421287</v>
+        <v>421457</v>
       </c>
       <c r="R18" t="n">
-        <v>7041560</v>
+        <v>7041782</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,7 +2597,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130269230</v>
+        <v>130269229</v>
       </c>
       <c r="B19" t="n">
         <v>57852</v>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421457</v>
+        <v>421474</v>
       </c>
       <c r="R19" t="n">
-        <v>7041782</v>
+        <v>7041778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130269229</v>
+        <v>130269253</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421474</v>
+        <v>421511</v>
       </c>
       <c r="R20" t="n">
-        <v>7041778</v>
+        <v>7041768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269238</v>
+        <v>130269254</v>
       </c>
       <c r="B24" t="n">
-        <v>91777</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,19 +3118,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3138,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421547</v>
+        <v>421471</v>
       </c>
       <c r="R24" t="n">
-        <v>7041796</v>
+        <v>7041708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,6 +3178,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269254</v>
+        <v>130269238</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>91778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3211,23 +3220,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3235,10 +3240,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421471</v>
+        <v>421547</v>
       </c>
       <c r="R25" t="n">
-        <v>7041708</v>
+        <v>7041796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,11 +3276,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269234</v>
+        <v>130269244</v>
       </c>
       <c r="B29" t="n">
-        <v>91771</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421319</v>
+        <v>421242</v>
       </c>
       <c r="R29" t="n">
-        <v>7041510</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,6 +3679,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3807,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130269244</v>
+        <v>130269234</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>91772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3818,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3842,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421242</v>
+        <v>421319</v>
       </c>
       <c r="R31" t="n">
-        <v>7041553</v>
+        <v>7041510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,11 +3883,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4215,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130269236</v>
+        <v>130269231</v>
       </c>
       <c r="B35" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4226,19 +4226,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4246,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421465</v>
+        <v>421458</v>
       </c>
       <c r="R35" t="n">
-        <v>7041769</v>
+        <v>7041835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4282,6 +4286,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4308,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269252</v>
+        <v>130269223</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4319,21 +4328,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4343,10 +4352,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421539</v>
+        <v>421322</v>
       </c>
       <c r="R36" t="n">
-        <v>7041777</v>
+        <v>7041512</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4392,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,10 +4419,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269223</v>
+        <v>130269236</v>
       </c>
       <c r="B37" t="n">
-        <v>57852</v>
+        <v>91778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4421,23 +4430,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4445,10 +4450,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421322</v>
+        <v>421465</v>
       </c>
       <c r="R37" t="n">
-        <v>7041512</v>
+        <v>7041769</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4481,11 +4486,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,10 +4512,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269231</v>
+        <v>130269252</v>
       </c>
       <c r="B38" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421458</v>
+        <v>421539</v>
       </c>
       <c r="R38" t="n">
-        <v>7041835</v>
+        <v>7041777</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130269237</v>
+        <v>130269245</v>
       </c>
       <c r="B15" t="n">
-        <v>91778</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,19 +2209,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2229,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421457</v>
+        <v>421197</v>
       </c>
       <c r="R15" t="n">
-        <v>7041831</v>
+        <v>7041597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,6 +2269,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130269245</v>
+        <v>130269237</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>91779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,23 +2311,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421197</v>
+        <v>421457</v>
       </c>
       <c r="R16" t="n">
-        <v>7041597</v>
+        <v>7041831</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,11 +2367,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3212,7 +3212,7 @@
         <v>130269238</v>
       </c>
       <c r="B25" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269244</v>
+        <v>130269234</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>91773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421242</v>
+        <v>421319</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,11 +3679,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,7 +3705,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130269247</v>
+        <v>130269244</v>
       </c>
       <c r="B30" t="n">
         <v>79209</v>
@@ -3745,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421218</v>
+        <v>421242</v>
       </c>
       <c r="R30" t="n">
-        <v>7041644</v>
+        <v>7041553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3780,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130269234</v>
+        <v>130269247</v>
       </c>
       <c r="B31" t="n">
-        <v>91772</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,21 +3818,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3842,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421319</v>
+        <v>421218</v>
       </c>
       <c r="R31" t="n">
-        <v>7041510</v>
+        <v>7041644</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,6 +3878,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,7 +4011,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130269243</v>
+        <v>130269251</v>
       </c>
       <c r="B33" t="n">
         <v>79209</v>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421168</v>
+        <v>421531</v>
       </c>
       <c r="R33" t="n">
-        <v>7041110</v>
+        <v>7041803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130269251</v>
+        <v>130269243</v>
       </c>
       <c r="B34" t="n">
         <v>79209</v>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421531</v>
+        <v>421168</v>
       </c>
       <c r="R34" t="n">
-        <v>7041803</v>
+        <v>7041110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4215,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130269231</v>
+        <v>130269252</v>
       </c>
       <c r="B35" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4226,21 +4226,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421458</v>
+        <v>421539</v>
       </c>
       <c r="R35" t="n">
-        <v>7041835</v>
+        <v>7041777</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4317,7 +4317,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269223</v>
+        <v>130269231</v>
       </c>
       <c r="B36" t="n">
         <v>57852</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421322</v>
+        <v>421458</v>
       </c>
       <c r="R36" t="n">
-        <v>7041512</v>
+        <v>7041835</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269236</v>
+        <v>130269223</v>
       </c>
       <c r="B37" t="n">
-        <v>91778</v>
+        <v>57852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4430,19 +4430,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4450,10 +4454,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421465</v>
+        <v>421322</v>
       </c>
       <c r="R37" t="n">
-        <v>7041769</v>
+        <v>7041512</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4486,6 +4490,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,10 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269252</v>
+        <v>130269236</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>91779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,23 +4532,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4547,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421539</v>
+        <v>421465</v>
       </c>
       <c r="R38" t="n">
-        <v>7041777</v>
+        <v>7041769</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4583,11 +4588,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130269245</v>
+        <v>130269237</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>91781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,23 +2209,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2233,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421197</v>
+        <v>421457</v>
       </c>
       <c r="R15" t="n">
-        <v>7041597</v>
+        <v>7041831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,11 +2265,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130269237</v>
+        <v>130269245</v>
       </c>
       <c r="B16" t="n">
-        <v>91779</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2311,19 +2302,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2331,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421457</v>
+        <v>421197</v>
       </c>
       <c r="R16" t="n">
-        <v>7041831</v>
+        <v>7041597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,6 +2362,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130269221</v>
+        <v>130269253</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,21 +2404,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421287</v>
+        <v>421511</v>
       </c>
       <c r="R17" t="n">
-        <v>7041560</v>
+        <v>7041768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130269230</v>
+        <v>130269221</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421457</v>
+        <v>421287</v>
       </c>
       <c r="R18" t="n">
-        <v>7041782</v>
+        <v>7041560</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130269229</v>
+        <v>130269230</v>
       </c>
       <c r="B19" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421474</v>
+        <v>421457</v>
       </c>
       <c r="R19" t="n">
-        <v>7041778</v>
+        <v>7041782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130269253</v>
+        <v>130269229</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421511</v>
+        <v>421474</v>
       </c>
       <c r="R20" t="n">
-        <v>7041768</v>
+        <v>7041778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,7 +2804,7 @@
         <v>130269250</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>130269246</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>130269232</v>
       </c>
       <c r="B23" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269254</v>
+        <v>130269228</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,21 +3118,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421471</v>
+        <v>421450</v>
       </c>
       <c r="R24" t="n">
-        <v>7041708</v>
+        <v>7041763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269238</v>
+        <v>130269254</v>
       </c>
       <c r="B25" t="n">
-        <v>91779</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,19 +3220,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3240,10 +3244,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421547</v>
+        <v>421471</v>
       </c>
       <c r="R25" t="n">
-        <v>7041796</v>
+        <v>7041708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,6 +3280,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,10 +3311,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130269228</v>
+        <v>130269238</v>
       </c>
       <c r="B26" t="n">
-        <v>57852</v>
+        <v>91781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,23 +3322,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3337,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421450</v>
+        <v>421547</v>
       </c>
       <c r="R26" t="n">
-        <v>7041763</v>
+        <v>7041796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3373,11 +3378,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,7 +3407,7 @@
         <v>130269227</v>
       </c>
       <c r="B27" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>130269248</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>130269234</v>
       </c>
       <c r="B29" t="n">
-        <v>91773</v>
+        <v>91775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>130269244</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>130269247</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>130269226</v>
       </c>
       <c r="B32" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>130269251</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>130269243</v>
       </c>
       <c r="B34" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>130269252</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269231</v>
+        <v>130269236</v>
       </c>
       <c r="B36" t="n">
-        <v>57852</v>
+        <v>91781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4328,23 +4328,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4352,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421458</v>
+        <v>421465</v>
       </c>
       <c r="R36" t="n">
-        <v>7041835</v>
+        <v>7041769</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,11 +4384,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4419,10 +4410,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269223</v>
+        <v>130269231</v>
       </c>
       <c r="B37" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421322</v>
+        <v>421458</v>
       </c>
       <c r="R37" t="n">
-        <v>7041512</v>
+        <v>7041835</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4521,10 +4512,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269236</v>
+        <v>130269223</v>
       </c>
       <c r="B38" t="n">
-        <v>91779</v>
+        <v>57854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,19 +4523,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4552,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421465</v>
+        <v>421322</v>
       </c>
       <c r="R38" t="n">
-        <v>7041769</v>
+        <v>7041512</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4588,6 +4583,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130269237</v>
+        <v>130269245</v>
       </c>
       <c r="B15" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,19 +2209,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2229,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421457</v>
+        <v>421197</v>
       </c>
       <c r="R15" t="n">
-        <v>7041831</v>
+        <v>7041597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,6 +2269,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130269245</v>
+        <v>130269237</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,23 +2311,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421197</v>
+        <v>421457</v>
       </c>
       <c r="R16" t="n">
-        <v>7041597</v>
+        <v>7041831</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,11 +2367,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269228</v>
+        <v>130269254</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,21 +3118,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421450</v>
+        <v>421471</v>
       </c>
       <c r="R24" t="n">
-        <v>7041763</v>
+        <v>7041708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269254</v>
+        <v>130269238</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,23 +3220,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3244,10 +3240,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421471</v>
+        <v>421547</v>
       </c>
       <c r="R25" t="n">
-        <v>7041708</v>
+        <v>7041796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,11 +3276,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3311,10 +3302,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130269238</v>
+        <v>130269228</v>
       </c>
       <c r="B26" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,19 +3313,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3342,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421547</v>
+        <v>421450</v>
       </c>
       <c r="R26" t="n">
-        <v>7041796</v>
+        <v>7041763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,6 +3373,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269234</v>
+        <v>130269244</v>
       </c>
       <c r="B29" t="n">
-        <v>91775</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421319</v>
+        <v>421242</v>
       </c>
       <c r="R29" t="n">
-        <v>7041510</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,6 +3679,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3705,7 +3710,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130269244</v>
+        <v>130269247</v>
       </c>
       <c r="B30" t="n">
         <v>79211</v>
@@ -3740,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421242</v>
+        <v>421218</v>
       </c>
       <c r="R30" t="n">
-        <v>7041553</v>
+        <v>7041644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,7 +3785,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3807,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130269247</v>
+        <v>130269234</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>91775</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3818,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3842,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421218</v>
+        <v>421319</v>
       </c>
       <c r="R31" t="n">
-        <v>7041644</v>
+        <v>7041510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,11 +3883,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269254</v>
+        <v>130269228</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,21 +3118,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421471</v>
+        <v>421450</v>
       </c>
       <c r="R24" t="n">
-        <v>7041708</v>
+        <v>7041763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269238</v>
+        <v>130269254</v>
       </c>
       <c r="B25" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,19 +3220,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3240,10 +3244,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421547</v>
+        <v>421471</v>
       </c>
       <c r="R25" t="n">
-        <v>7041796</v>
+        <v>7041708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,6 +3280,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,10 +3311,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130269228</v>
+        <v>130269238</v>
       </c>
       <c r="B26" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,23 +3322,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3337,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421450</v>
+        <v>421547</v>
       </c>
       <c r="R26" t="n">
-        <v>7041763</v>
+        <v>7041796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3373,11 +3378,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4317,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269236</v>
+        <v>130269231</v>
       </c>
       <c r="B36" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4328,19 +4328,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4348,10 +4352,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421465</v>
+        <v>421458</v>
       </c>
       <c r="R36" t="n">
-        <v>7041769</v>
+        <v>7041835</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4384,6 +4388,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,7 +4419,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269231</v>
+        <v>130269223</v>
       </c>
       <c r="B37" t="n">
         <v>57854</v>
@@ -4445,10 +4454,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421458</v>
+        <v>421322</v>
       </c>
       <c r="R37" t="n">
-        <v>7041835</v>
+        <v>7041512</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,10 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269223</v>
+        <v>130269236</v>
       </c>
       <c r="B38" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,23 +4532,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4547,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421322</v>
+        <v>421465</v>
       </c>
       <c r="R38" t="n">
-        <v>7041512</v>
+        <v>7041769</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4583,11 +4588,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269228</v>
+        <v>130269238</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,23 +3118,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3142,10 +3138,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421450</v>
+        <v>421547</v>
       </c>
       <c r="R24" t="n">
-        <v>7041763</v>
+        <v>7041796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3178,11 +3174,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,10 +3302,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130269238</v>
+        <v>130269228</v>
       </c>
       <c r="B26" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,19 +3313,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3342,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421547</v>
+        <v>421450</v>
       </c>
       <c r="R26" t="n">
-        <v>7041796</v>
+        <v>7041763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,6 +3373,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269244</v>
+        <v>130269234</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>91775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421242</v>
+        <v>421319</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,11 +3679,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,7 +3705,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130269247</v>
+        <v>130269244</v>
       </c>
       <c r="B30" t="n">
         <v>79211</v>
@@ -3745,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421218</v>
+        <v>421242</v>
       </c>
       <c r="R30" t="n">
-        <v>7041644</v>
+        <v>7041553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3780,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130269234</v>
+        <v>130269247</v>
       </c>
       <c r="B31" t="n">
-        <v>91775</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,21 +3818,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3842,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421319</v>
+        <v>421218</v>
       </c>
       <c r="R31" t="n">
-        <v>7041510</v>
+        <v>7041644</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,6 +3878,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4317,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269231</v>
+        <v>130269236</v>
       </c>
       <c r="B36" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4328,23 +4328,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4352,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421458</v>
+        <v>421465</v>
       </c>
       <c r="R36" t="n">
-        <v>7041835</v>
+        <v>7041769</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,11 +4384,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4419,7 +4410,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269223</v>
+        <v>130269231</v>
       </c>
       <c r="B37" t="n">
         <v>57854</v>
@@ -4454,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421322</v>
+        <v>421458</v>
       </c>
       <c r="R37" t="n">
-        <v>7041512</v>
+        <v>7041835</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4521,10 +4512,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269236</v>
+        <v>130269223</v>
       </c>
       <c r="B38" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,19 +4523,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4552,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421465</v>
+        <v>421322</v>
       </c>
       <c r="R38" t="n">
-        <v>7041769</v>
+        <v>7041512</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4588,6 +4583,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269238</v>
+        <v>130269254</v>
       </c>
       <c r="B24" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,19 +3118,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3138,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421547</v>
+        <v>421471</v>
       </c>
       <c r="R24" t="n">
-        <v>7041796</v>
+        <v>7041708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,6 +3178,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269254</v>
+        <v>130269228</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3211,21 +3220,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3235,10 +3244,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421471</v>
+        <v>421450</v>
       </c>
       <c r="R25" t="n">
-        <v>7041708</v>
+        <v>7041763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,7 +3284,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,10 +3311,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130269228</v>
+        <v>130269238</v>
       </c>
       <c r="B26" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,23 +3322,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3337,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421450</v>
+        <v>421547</v>
       </c>
       <c r="R26" t="n">
-        <v>7041763</v>
+        <v>7041796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3373,11 +3378,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -2201,7 +2201,7 @@
         <v>130269245</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130269237</v>
       </c>
       <c r="B16" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>130269253</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130269221</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>130269230</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>130269229</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130269250</v>
+        <v>130269246</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421267</v>
+        <v>421193</v>
       </c>
       <c r="R21" t="n">
-        <v>7041668</v>
+        <v>7041705</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130269246</v>
+        <v>130269250</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421193</v>
+        <v>421267</v>
       </c>
       <c r="R22" t="n">
-        <v>7041705</v>
+        <v>7041668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>130269232</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269254</v>
+        <v>130269228</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,21 +3118,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421471</v>
+        <v>421450</v>
       </c>
       <c r="R24" t="n">
-        <v>7041708</v>
+        <v>7041763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269228</v>
+        <v>130269238</v>
       </c>
       <c r="B25" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,23 +3220,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3244,10 +3240,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421450</v>
+        <v>421547</v>
       </c>
       <c r="R25" t="n">
-        <v>7041763</v>
+        <v>7041796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,11 +3276,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3311,10 +3302,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130269238</v>
+        <v>130269254</v>
       </c>
       <c r="B26" t="n">
-        <v>91781</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,19 +3313,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3342,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421547</v>
+        <v>421471</v>
       </c>
       <c r="R26" t="n">
-        <v>7041796</v>
+        <v>7041708</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,6 +3373,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,7 +3407,7 @@
         <v>130269227</v>
       </c>
       <c r="B27" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>130269248</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269234</v>
+        <v>130269244</v>
       </c>
       <c r="B29" t="n">
-        <v>91775</v>
+        <v>79219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421319</v>
+        <v>421242</v>
       </c>
       <c r="R29" t="n">
-        <v>7041510</v>
+        <v>7041553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,6 +3679,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3705,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130269244</v>
+        <v>130269247</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421242</v>
+        <v>421218</v>
       </c>
       <c r="R30" t="n">
-        <v>7041553</v>
+        <v>7041644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,7 +3785,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3807,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130269247</v>
+        <v>130269234</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>91788</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3818,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3842,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421218</v>
+        <v>421319</v>
       </c>
       <c r="R31" t="n">
-        <v>7041644</v>
+        <v>7041510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,11 +3883,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3912,7 +3912,7 @@
         <v>130269226</v>
       </c>
       <c r="B32" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>130269251</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>130269243</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>130269252</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>130269236</v>
       </c>
       <c r="B36" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>130269231</v>
       </c>
       <c r="B37" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>130269223</v>
       </c>
       <c r="B38" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89584538</v>
+        <v>89584579</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421496.0172838716</v>
+        <v>421487</v>
       </c>
       <c r="R2" t="n">
-        <v>7042034.934251956</v>
+        <v>7041478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89584543</v>
+        <v>89584553</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421439.9129397727</v>
+        <v>421553</v>
       </c>
       <c r="R3" t="n">
-        <v>7041446.903843992</v>
+        <v>7041641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,50 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89584559</v>
+        <v>130269234</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärn, Jmt</t>
+          <t>Stor-Sättertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421550.780420415</v>
+        <v>421319</v>
       </c>
       <c r="R4" t="n">
-        <v>7041714.985647468</v>
+        <v>7041510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,31 +962,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89584579</v>
+        <v>89584536</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421487.2173269815</v>
+        <v>421427</v>
       </c>
       <c r="R5" t="n">
-        <v>7041477.915203343</v>
+        <v>7042224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,21 +1042,11 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,6 +1055,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89584575</v>
+        <v>89584545</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421371.2048817004</v>
+        <v>421534</v>
       </c>
       <c r="R6" t="n">
-        <v>7042198.863730462</v>
+        <v>7041545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,21 +1148,11 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,6 +1161,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,15 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89584565</v>
+        <v>89584564</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421372.1493885518</v>
+        <v>421534</v>
       </c>
       <c r="R7" t="n">
-        <v>7041439.189780109</v>
+        <v>7041616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1254,9 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89584536</v>
+        <v>89584572</v>
       </c>
       <c r="B8" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421426.8512369159</v>
+        <v>421544</v>
       </c>
       <c r="R8" t="n">
-        <v>7042223.852136237</v>
+        <v>7041700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1355,9 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,37 +1393,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89584564</v>
+        <v>89584556</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421534.0291829754</v>
+        <v>421369</v>
       </c>
       <c r="R9" t="n">
-        <v>7041616.192128117</v>
+        <v>7041430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,19 +1461,9 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,50 +1494,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89584566</v>
+        <v>130269243</v>
       </c>
       <c r="B10" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärn, Jmt</t>
+          <t>Stor-Sättertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421325.0575127905</v>
+        <v>421168</v>
       </c>
       <c r="R10" t="n">
-        <v>7041434.988962475</v>
+        <v>7041110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,22 +1559,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,66 +1584,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89584572</v>
+        <v>130269244</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärn, Jmt</t>
+          <t>Stor-Sättertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421544.1458833363</v>
+        <v>421242</v>
       </c>
       <c r="R11" t="n">
-        <v>7041699.95547199</v>
+        <v>7041553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,22 +1661,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,75 +1682,61 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89584553</v>
+        <v>130269245</v>
       </c>
       <c r="B12" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärn, Jmt</t>
+          <t>Stor-Sättertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421552.99135932</v>
+        <v>421197</v>
       </c>
       <c r="R12" t="n">
-        <v>7041641.197410068</v>
+        <v>7041597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,22 +1763,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,66 +1788,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89584563</v>
+        <v>130269246</v>
       </c>
       <c r="B13" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärn, Jmt</t>
+          <t>Stor-Sättertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421496.9115847631</v>
+        <v>421193</v>
       </c>
       <c r="R13" t="n">
-        <v>7042034.91222003</v>
+        <v>7041705</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,22 +1865,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,75 +1886,61 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89584556</v>
+        <v>130269247</v>
       </c>
       <c r="B14" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärn, Jmt</t>
+          <t>Stor-Sättertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421368.787359876</v>
+        <v>421218</v>
       </c>
       <c r="R14" t="n">
-        <v>7041429.88767274</v>
+        <v>7041644</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,22 +1967,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,30 +1992,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130269245</v>
+        <v>130269248</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2233,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421197</v>
+        <v>421263</v>
       </c>
       <c r="R15" t="n">
-        <v>7041597</v>
+        <v>7041605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2273,7 +2079,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,30 +2106,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130269237</v>
+        <v>130269249</v>
       </c>
       <c r="B16" t="n">
-        <v>91794</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2331,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421457</v>
+        <v>421381</v>
       </c>
       <c r="R16" t="n">
-        <v>7041831</v>
+        <v>7041494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,6 +2177,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,14 +2208,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130269253</v>
+        <v>130269250</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2428,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421511</v>
+        <v>421267</v>
       </c>
       <c r="R17" t="n">
-        <v>7041768</v>
+        <v>7041668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,32 +2310,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130269221</v>
+        <v>130269251</v>
       </c>
       <c r="B18" t="n">
-        <v>57862</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2530,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421287</v>
+        <v>421531</v>
       </c>
       <c r="R18" t="n">
-        <v>7041560</v>
+        <v>7041803</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2385,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,32 +2412,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130269230</v>
+        <v>130269252</v>
       </c>
       <c r="B19" t="n">
-        <v>57862</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2447,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421457</v>
+        <v>421539</v>
       </c>
       <c r="R19" t="n">
-        <v>7041782</v>
+        <v>7041777</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,7 +2487,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,32 +2514,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130269229</v>
+        <v>130269253</v>
       </c>
       <c r="B20" t="n">
-        <v>57862</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2549,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421474</v>
+        <v>421511</v>
       </c>
       <c r="R20" t="n">
-        <v>7041778</v>
+        <v>7041768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2589,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,14 +2616,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130269246</v>
+        <v>130269254</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2836,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421193</v>
+        <v>421471</v>
       </c>
       <c r="R21" t="n">
-        <v>7041705</v>
+        <v>7041708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,14 +2718,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130269250</v>
+        <v>130269255</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2938,10 +2753,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421267</v>
+        <v>421442</v>
       </c>
       <c r="R22" t="n">
-        <v>7041668</v>
+        <v>7041631</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,45 +2820,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130269232</v>
+        <v>89584563</v>
       </c>
       <c r="B23" t="n">
-        <v>57862</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärnen, Jmt</t>
+          <t>Stor-Sättertjärn, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421465</v>
+        <v>421497</v>
       </c>
       <c r="R23" t="n">
-        <v>7041678</v>
+        <v>7042035</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3070,17 +2885,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,61 +2901,70 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Rönn</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130269228</v>
+        <v>89584558</v>
       </c>
       <c r="B24" t="n">
-        <v>57862</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärnen, Jmt</t>
+          <t>Stor-Sättertjärn, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421450</v>
+        <v>421537</v>
       </c>
       <c r="R24" t="n">
-        <v>7041763</v>
+        <v>7041547</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,17 +2991,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,22 +3011,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130269238</v>
+        <v>130269221</v>
       </c>
       <c r="B25" t="n">
-        <v>91794</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,19 +3038,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3240,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421547</v>
+        <v>421287</v>
       </c>
       <c r="R25" t="n">
-        <v>7041796</v>
+        <v>7041560</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,6 +3098,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,10 +3129,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130269254</v>
+        <v>130269222</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,21 +3140,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3337,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421471</v>
+        <v>421331</v>
       </c>
       <c r="R26" t="n">
-        <v>7041708</v>
+        <v>7041478</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3204,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,10 +3231,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130269227</v>
+        <v>130269223</v>
       </c>
       <c r="B27" t="n">
-        <v>57862</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421346</v>
+        <v>421322</v>
       </c>
       <c r="R27" t="n">
-        <v>7041741</v>
+        <v>7041512</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3506,10 +3333,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130269248</v>
+        <v>130269224</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3517,21 +3344,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3541,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421263</v>
+        <v>421340</v>
       </c>
       <c r="R28" t="n">
-        <v>7041605</v>
+        <v>7041479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3581,7 +3408,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,10 +3435,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130269244</v>
+        <v>130269225</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421242</v>
+        <v>421385</v>
       </c>
       <c r="R29" t="n">
-        <v>7041553</v>
+        <v>7041502</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3683,7 +3510,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,10 +3537,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130269247</v>
+        <v>130269226</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,21 +3548,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421218</v>
+        <v>421267</v>
       </c>
       <c r="R30" t="n">
-        <v>7041644</v>
+        <v>7041662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3612,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3639,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130269234</v>
+        <v>130269227</v>
       </c>
       <c r="B31" t="n">
-        <v>91788</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,21 +3650,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3674,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421319</v>
+        <v>421346</v>
       </c>
       <c r="R31" t="n">
-        <v>7041510</v>
+        <v>7041741</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,6 +3710,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3909,10 +3741,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130269226</v>
+        <v>130269228</v>
       </c>
       <c r="B32" t="n">
-        <v>57862</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3944,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421267</v>
+        <v>421450</v>
       </c>
       <c r="R32" t="n">
-        <v>7041662</v>
+        <v>7041763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4011,10 +3843,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130269251</v>
+        <v>130269229</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +3854,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +3878,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421531</v>
+        <v>421474</v>
       </c>
       <c r="R33" t="n">
-        <v>7041803</v>
+        <v>7041778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,7 +3918,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130269243</v>
+        <v>130269230</v>
       </c>
       <c r="B34" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4124,21 +3956,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4148,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421168</v>
+        <v>421457</v>
       </c>
       <c r="R34" t="n">
-        <v>7041110</v>
+        <v>7041782</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4215,10 +4047,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130269252</v>
+        <v>130269231</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4226,21 +4058,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4250,10 +4082,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421539</v>
+        <v>421458</v>
       </c>
       <c r="R35" t="n">
-        <v>7041777</v>
+        <v>7041835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,7 +4122,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4317,10 +4149,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130269236</v>
+        <v>130269232</v>
       </c>
       <c r="B36" t="n">
-        <v>91794</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4328,19 +4160,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4351,7 +4187,7 @@
         <v>421465</v>
       </c>
       <c r="R36" t="n">
-        <v>7041769</v>
+        <v>7041678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4384,6 +4220,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,10 +4251,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130269231</v>
+        <v>130269233</v>
       </c>
       <c r="B37" t="n">
-        <v>57862</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4445,10 +4286,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421458</v>
+        <v>421454</v>
       </c>
       <c r="R37" t="n">
-        <v>7041835</v>
+        <v>7041639</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,45 +4353,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130269223</v>
+        <v>89584566</v>
       </c>
       <c r="B38" t="n">
-        <v>57862</v>
+        <v>99456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Sättertjärnen, Jmt</t>
+          <t>Stor-Sättertjärn, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421322</v>
+        <v>421325</v>
       </c>
       <c r="R38" t="n">
-        <v>7041512</v>
+        <v>7041435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4577,17 +4418,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,15 +4438,120 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>89584538</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stor-Sättertjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>421496</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7042035</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56865-2025 artfynd.xlsx
+++ b/artfynd/A 56865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584579</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584553</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269234</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584536</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584545</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584564</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584572</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584556</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269243</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269244</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1797,6 +1852,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269245</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269246</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269247</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269248</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2205,6 +2280,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269249</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269250</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269251</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269252</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269253</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2715,6 +2815,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269254</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2817,6 +2922,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269255</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2923,6 +3033,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584563</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3024,6 +3139,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584558</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3126,6 +3246,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269221</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3228,6 +3353,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269222</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3330,6 +3460,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269223</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3432,6 +3567,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269224</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3534,6 +3674,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269225</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3636,6 +3781,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269226</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3738,6 +3888,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269227</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3840,6 +3995,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269228</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3942,6 +4102,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269229</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4044,6 +4209,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269230</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4146,6 +4316,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269231</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4248,6 +4423,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269232</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4350,6 +4530,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130269233</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4451,6 +4636,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584566</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4552,8 +4742,53 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>